--- a/artfynd/A 10713-2025 artfynd.xlsx
+++ b/artfynd/A 10713-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98289705</v>
+        <v>98289694</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516447.9336456363</v>
+        <v>516481</v>
       </c>
       <c r="R2" t="n">
-        <v>6677564.489424353</v>
+        <v>6677665</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,24 +747,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lockläte   FLD0081 (Calluna AB) NVI</t>
+          <t>FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98289775</v>
+        <v>98289723</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516376.6901814259</v>
+        <v>516382</v>
       </c>
       <c r="R3" t="n">
-        <v>6677586.520569154</v>
+        <v>6677597</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,24 +853,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
+          <t>FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98289723</v>
+        <v>98289737</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516382.6112428986</v>
+        <v>516504</v>
       </c>
       <c r="R4" t="n">
-        <v>6677597.474215617</v>
+        <v>6677631</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,24 +959,14 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>FLD0081 (Calluna AB) NVI</t>
+          <t>Flera artrena tuvor  FLD0081 (Calluna AB) NVI</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,6 +990,536 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98289713</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516421</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6677598</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt längs bäcken   FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>98289715</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516454</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6677653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98289775</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516377</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6677587</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnagspår   FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98289705</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6677564</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lockläte   FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>98289531</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skissklack-Siksjöberget-Daldammsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516377</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6677609</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-11-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-11-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnagspår FLD0081 (Calluna AB) NVI</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
